--- a/data/trans_orig/P33B1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023</t>
+          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>40163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>47684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53920</t>
+          <t>54704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81050</t>
+          <t>83076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50189</t>
+          <t>50564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77726</t>
+          <t>76971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>244887</t>
+          <t>245255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273173</t>
+          <t>273163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196038</t>
+          <t>195613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220906</t>
+          <t>220676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>450122</t>
+          <t>449023</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>486898</t>
+          <t>486944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38823</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,47 +1349,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>43069</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>30106</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>60475</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>43069</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>30493</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>60925</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44997</t>
+          <t>44531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42866</t>
+          <t>43474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71367</t>
+          <t>71798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87165</t>
+          <t>90341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135259</t>
+          <t>136303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110492</t>
+          <t>109162</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142002</t>
+          <t>142336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207927</t>
+          <t>204660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267049</t>
+          <t>262806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>340528</t>
+          <t>339181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>393885</t>
+          <t>390046</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314483</t>
+          <t>312310</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>350685</t>
+          <t>349185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665172</t>
+          <t>668122</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>733258</t>
+          <t>731236</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30017</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>47966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46184</t>
+          <t>46045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71747</t>
+          <t>70553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47400</t>
+          <t>48474</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50083</t>
+          <t>49976</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>76135</t>
+          <t>75080</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>30688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>52166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54591</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77959</t>
+          <t>77197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>91662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120654</t>
+          <t>121477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217490</t>
+          <t>217151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247483</t>
+          <t>247220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188925</t>
+          <t>191672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220179</t>
+          <t>221735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417217</t>
+          <t>418250</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>459026</t>
+          <t>459856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60247</t>
+          <t>61082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47524</t>
+          <t>46406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87223</t>
+          <t>85171</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55965</t>
+          <t>57520</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>45698</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83783</t>
+          <t>84884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30959</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57822</t>
+          <t>58932</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50446</t>
+          <t>47455</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106692</t>
+          <t>107526</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>92637</t>
+          <t>88839</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>151502</t>
+          <t>152531</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>206019</t>
+          <t>203854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242099</t>
+          <t>241586</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>261960</t>
+          <t>261134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>374052</t>
+          <t>377312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>488652</t>
+          <t>491221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>601343</t>
+          <t>603552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29591</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115713</t>
+          <t>114672</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137642</t>
+          <t>137426</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147797</t>
+          <t>146438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>165287</t>
+          <t>164953</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>269918</t>
+          <t>268497</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297511</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>28624</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>37730</t>
+          <t>38061</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>54592</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>78765</t>
+          <t>80851</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53407</t>
+          <t>54682</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55364</t>
+          <t>54785</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80046</t>
+          <t>78903</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50049</t>
+          <t>50238</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>37912</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56209</t>
+          <t>57361</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>72038</t>
+          <t>72225</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>98100</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>187568</t>
+          <t>185947</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>212912</t>
+          <t>211817</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>137975</t>
+          <t>135775</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>162536</t>
+          <t>162054</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>333226</t>
+          <t>333283</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>367656</t>
+          <t>367854</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>47290</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>30709</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>91065</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>60089</t>
+          <t>62353</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>121899</t>
+          <t>121182</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>64301</t>
+          <t>65360</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>36582</t>
+          <t>35646</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>104775</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>70995</t>
+          <t>78412</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>148460</t>
+          <t>149629</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>94519</t>
+          <t>94558</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>138374</t>
+          <t>139003</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>72943</t>
+          <t>65128</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>185877</t>
+          <t>187504</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>158960</t>
+          <t>162612</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>299834</t>
+          <t>303928</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>404803</t>
+          <t>401414</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>458568</t>
+          <t>457861</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>476451</t>
+          <t>479049</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>699453</t>
+          <t>718934</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>923150</t>
+          <t>918242</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1193131</t>
+          <t>1163941</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>48832</t>
+          <t>50696</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>153619</t>
+          <t>155836</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>149194</t>
+          <t>148325</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>183993</t>
+          <t>184454</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>163393</t>
+          <t>167091</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>328338</t>
+          <t>330018</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>47232</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>47570</t>
+          <t>47035</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>69360</t>
+          <t>69416</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54696</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>109977</t>
+          <t>111413</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>53337</t>
+          <t>56641</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>177872</t>
+          <t>179304</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>133063</t>
+          <t>134827</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>170114</t>
+          <t>170773</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>176376</t>
+          <t>168777</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>336762</t>
+          <t>337356</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>561218</t>
+          <t>558816</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>809185</t>
+          <t>808100</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>318087</t>
+          <t>318200</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>366385</t>
+          <t>362818</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>882575</t>
+          <t>882118</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1243834</t>
+          <t>1260218</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>172956</t>
+          <t>168068</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>250616</t>
+          <t>249579</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>295852</t>
+          <t>293250</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>400890</t>
+          <t>403360</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>504513</t>
+          <t>503996</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>631272</t>
+          <t>634570</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>156975</t>
+          <t>159525</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>235374</t>
+          <t>235524</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>279624</t>
+          <t>279869</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>377380</t>
+          <t>381421</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>472990</t>
+          <t>467339</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>595723</t>
+          <t>594319</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>476973</t>
+          <t>473725</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>687423</t>
+          <t>687018</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>638320</t>
+          <t>665901</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>874498</t>
+          <t>877771</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1242481</t>
+          <t>1231754</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1527666</t>
+          <t>1532344</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2323366</t>
+          <t>2317871</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2677144</t>
+          <t>2670482</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2027298</t>
+          <t>2020954</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2480848</t>
+          <t>2453799</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4407633</t>
+          <t>4389629</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4928401</t>
+          <t>4883507</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>26947</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40163</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39510</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31591</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47684</t>
+          <t>51854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>67017</t>
+          <t>69699</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54704</t>
+          <t>58084</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83076</t>
+          <t>84434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>28179</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>39694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39444</t>
+          <t>47594</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>36636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>61497</t>
+          <t>75773</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76971</t>
+          <t>91654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>260333</t>
+          <t>262244</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>245255</t>
+          <t>247902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273163</t>
+          <t>274960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>208540</t>
+          <t>223235</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195613</t>
+          <t>209093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220676</t>
+          <t>236365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>468872</t>
+          <t>485479</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449023</t>
+          <t>465706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>486944</t>
+          <t>502974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20308</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35860</t>
+          <t>33316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>22957</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>31341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>42772</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>31002</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60475</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>20627</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>35877</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44531</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55258</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43474</t>
+          <t>45030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71798</t>
+          <t>74100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>114686</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90341</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136303</t>
+          <t>139939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125864</t>
+          <t>136162</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109162</t>
+          <t>118919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142336</t>
+          <t>155663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>236027</t>
+          <t>250848</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204660</t>
+          <t>221376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262806</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>367474</t>
+          <t>375519</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>339181</t>
+          <t>348377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>390046</t>
+          <t>399435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>331532</t>
+          <t>351498</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312310</t>
+          <t>331496</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349185</t>
+          <t>370926</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>699006</t>
+          <t>727017</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>668122</t>
+          <t>691911</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>731236</t>
+          <t>760092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38198</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>30321</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47966</t>
+          <t>49446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>58368</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46045</t>
+          <t>47151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70553</t>
+          <t>71488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34497</t>
+          <t>35148</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37852</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30092</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48474</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61434</t>
+          <t>62928</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>49355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>75080</t>
+          <t>76895</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2089,22 +2089,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30688</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>51809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65292</t>
+          <t>66708</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>78768</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>105264</t>
+          <t>106925</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91662</t>
+          <t>92370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121477</t>
+          <t>124388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>232875</t>
+          <t>231860</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217151</t>
+          <t>218086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247220</t>
+          <t>246597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>206716</t>
+          <t>211186</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191672</t>
+          <t>196268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>221735</t>
+          <t>225908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>439591</t>
+          <t>443046</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418250</t>
+          <t>420860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>459856</t>
+          <t>462826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,95%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>348059</t>
+          <t>355274</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348059</t>
+          <t>355274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348059</t>
+          <t>355274</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>664109</t>
+          <t>671267</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>664109</t>
+          <t>671267</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>664109</t>
+          <t>671267</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>39155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43913</t>
+          <t>47863</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26682</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>61767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46406</t>
+          <t>58384</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85171</t>
+          <t>94114</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>24373</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41855</t>
+          <t>47218</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>37354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57520</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>71592</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45698</t>
+          <t>58190</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84884</t>
+          <t>89530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42801</t>
+          <t>50760</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>37904</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58932</t>
+          <t>70552</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82709</t>
+          <t>89589</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47455</t>
+          <t>75796</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107526</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>125510</t>
+          <t>140350</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88839</t>
+          <t>119221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>152531</t>
+          <t>163101</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>224935</t>
+          <t>272739</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203854</t>
+          <t>251123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241586</t>
+          <t>291307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>307241</t>
+          <t>237290</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>261134</t>
+          <t>217371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>377312</t>
+          <t>256589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>532176</t>
+          <t>510030</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>491221</t>
+          <t>482135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>603552</t>
+          <t>539458</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>31450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>127481</t>
+          <t>143354</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114672</t>
+          <t>129552</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137426</t>
+          <t>154558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>156735</t>
+          <t>168773</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146438</t>
+          <t>157574</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164953</t>
+          <t>177424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>284216</t>
+          <t>312127</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268497</t>
+          <t>295332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>326968</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>47766</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>36602</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>60886</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28671</t>
+          <t>33019</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>43574</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>66268</t>
+          <t>80785</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>65449</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>80851</t>
+          <t>96093</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17900</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>13697</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32307</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>56652</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>65903</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54785</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>78903</t>
+          <t>79779</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50238</t>
+          <t>48737</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>47764</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37912</t>
+          <t>38853</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>57361</t>
+          <t>57130</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>85355</t>
+          <t>86232</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>72225</t>
+          <t>72651</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>98100</t>
+          <t>99406</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>201079</t>
+          <t>202155</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>185947</t>
+          <t>189144</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>211817</t>
+          <t>213157</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>149813</t>
+          <t>153095</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135775</t>
+          <t>140009</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>162054</t>
+          <t>166071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>350892</t>
+          <t>355250</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>333283</t>
+          <t>337632</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>367854</t>
+          <t>372746</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>31255</t>
+          <t>34981</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>24795</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46977</t>
+          <t>50385</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>65546</t>
+          <t>82760</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30709</t>
+          <t>68083</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>92540</t>
+          <t>101054</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>96801</t>
+          <t>117741</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>62353</t>
+          <t>99144</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>121182</t>
+          <t>140143</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>52745</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>38693</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>65360</t>
+          <t>70611</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>73551</t>
+          <t>90834</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>35646</t>
+          <t>75004</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>104775</t>
+          <t>108983</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>118735</t>
+          <t>143579</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>78412</t>
+          <t>121217</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>149629</t>
+          <t>168769</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>114798</t>
+          <t>132077</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>94558</t>
+          <t>111300</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>139003</t>
+          <t>157222</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>135751</t>
+          <t>161280</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>140236</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>187504</t>
+          <t>182026</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>250549</t>
+          <t>293357</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>162612</t>
+          <t>260322</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>303928</t>
+          <t>323620</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>432012</t>
+          <t>498802</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>401414</t>
+          <t>468930</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>457861</t>
+          <t>524821</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>574417</t>
+          <t>437183</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>479049</t>
+          <t>412390</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>718934</t>
+          <t>462651</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1006428</t>
+          <t>935985</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>918242</t>
+          <t>894825</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1163941</t>
+          <t>972550</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>107943</t>
+          <t>120954</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>50696</t>
+          <t>102440</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>155836</t>
+          <t>140854</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>165402</t>
+          <t>189798</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>148325</t>
+          <t>168738</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>184454</t>
+          <t>209803</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>273345</t>
+          <t>310752</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>167091</t>
+          <t>284983</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>330018</t>
+          <t>342149</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>33613</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47232</t>
+          <t>44581</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>66150</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>47035</t>
+          <t>53772</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>69416</t>
+          <t>80162</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>87567</t>
+          <t>99763</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>84048</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>111413</t>
+          <t>117667</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>125331</t>
+          <t>142988</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>56641</t>
+          <t>122095</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>179304</t>
+          <t>166034</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>151480</t>
+          <t>176568</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>134827</t>
+          <t>156897</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>170773</t>
+          <t>197489</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>276812</t>
+          <t>319557</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>168777</t>
+          <t>288332</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>337356</t>
+          <t>348382</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>665177</t>
+          <t>500517</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>558816</t>
+          <t>471329</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>808100</t>
+          <t>528974</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>341211</t>
+          <t>398092</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>318200</t>
+          <t>374546</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>362818</t>
+          <t>427315</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1006388</t>
+          <t>898609</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>882118</t>
+          <t>858269</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1260218</t>
+          <t>939750</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>215365</t>
+          <t>235280</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>204381</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>249579</t>
+          <t>265608</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>364310</t>
+          <t>412114</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>293250</t>
+          <t>378483</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>403360</t>
+          <t>446216</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>579675</t>
+          <t>647393</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>503996</t>
+          <t>604744</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>634570</t>
+          <t>696240</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>214067</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>159525</t>
+          <t>187792</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>235524</t>
+          <t>246156</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>341750</t>
+          <t>381879</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>279869</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>381421</t>
+          <t>411565</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>542628</t>
+          <t>595947</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>467339</t>
+          <t>551476</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>594319</t>
+          <t>640959</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>621062</t>
+          <t>690730</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>473725</t>
+          <t>646410</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>687018</t>
+          <t>746665</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>804167</t>
+          <t>894439</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>665901</t>
+          <t>852398</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>877771</t>
+          <t>938218</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1425229</t>
+          <t>1585169</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1231754</t>
+          <t>1519010</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1532344</t>
+          <t>1652378</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2421482</t>
+          <t>2391603</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2317871</t>
+          <t>2335211</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2670482</t>
+          <t>2447533</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2148139</t>
+          <t>2044599</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2020954</t>
+          <t>1994367</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2453799</t>
+          <t>2098085</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4569622</t>
+          <t>4436201</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4389629</t>
+          <t>4357154</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4883507</t>
+          <t>4515442</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
